--- a/Eye_Qing_Guang_research/01_Background_and_Literature/【大数据挑战赛·常见问题参考】2026年第八届全国高校计算机能力挑战赛.xlsx
+++ b/Eye_Qing_Guang_research/01_Background_and_Literature/【大数据挑战赛·常见问题参考】2026年第八届全国高校计算机能力挑战赛.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t/>
   </si>
@@ -266,6 +266,33 @@
 本次竞赛赛题方将从严处置作弊行为。一经查实，相关人员提交的全部结果均予作废，不接受任何申辩理由。请各位参赛选手珍惜参赛机会。</t>
   </si>
   <si>
+    <t>可以用外部预训练权重初始化，但不包含医学类预训练模型</t>
+  </si>
+  <si>
+    <t>1. 可以用外部预训练权重初始化，但不包含医学类预训练模型；2. 测试集和验证集的图片不能参与训练，以免造成模型选择偏差</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>可以用外部预训练权重初始化，但不包含医学类预训练模型，保证在给定类型gpu上的推理耗时就可以</t>
+  </si>
+  <si>
+    <t>1. 外部标注数据指模型训练时候引入的外部有标注数据集，但可以基于原始训练数据进行数据增强；2. 可以用外部预训练权重初始化，但不包含医学类预训练模型；</t>
+  </si>
+  <si>
+    <t>1. 可以用外部预训练权重初始化，但不包含医学类预训练模型；2. 测试集图片不能参与训练，以免造成模型选择偏差</t>
+  </si>
+  <si>
+    <t>p'ro'bability</t>
+  </si>
+  <si>
+    <t>主指标用probability</t>
+  </si>
+  <si>
+    <t>1. 可以用外部预训练权重初始化，但不包含医学类预训练模型；2. 验证集是否参与训练，由选手结合实际需求自主选择。验证集一经并入训练，不得再用于早停、checkpoint 选择或任何阈值、超参数调整，此类选择须在并入训练前完成。</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="1"/>
@@ -673,6 +700,88 @@
         <u val="none"/>
       </rPr>
       <t>根据大赛规则，区域赛/省赛阶段仅依据CSV文件的准确性进行排名。区域赛/省赛结束后，赛题方将要求所有晋级选手提交训练模型，用于复现校验模型是否满足100ms的性能要求，并同步开展合规性与反作弊审查；如有必要，还需提交训练过程文档以复现结果。校验通过后确认晋级；若未达标，晋级名次将依次顺延。</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FF000000"/>
+        <sz val="10"/>
+        <u val="none"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FFFF0000"/>
+        <sz val="10"/>
+        <u val="none"/>
+      </rPr>
+      <t>本次竞赛赛题方将从严处置作弊行为。一经查实，相关人员提交的全部结果均予作废，不接受任何申辩理由。请各位参赛选手珍惜参赛机会。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="1"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FFFF0000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
+      <t>注意：</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FF000000"/>
+        <sz val="10"/>
+        <u val="none"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="1"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FFFF0000"/>
+        <sz val="10"/>
+        <u val="none"/>
+      </rPr>
+      <t>初赛提交的csv格式要和提交样例相同。</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FF000000"/>
+        <sz val="10"/>
+        <u val="none"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FFFF0000"/>
+        <sz val="10"/>
+        <u val="none"/>
+      </rPr>
+      <t>根据大赛规则，区域赛/省赛阶段仅依据CSV文件的准确性进行排名。区域赛/省赛结束前，请所有参赛队伍选手提交训练模型，用于复现校验模型是否满足100ms的性能要求，并同步开展合规性与反作弊审查；如有必要，还需提交训练过程文档以复现结果。校验通过后确认晋级；若未达标，晋级名次将依次顺延。</t>
     </r>
     <r>
       <rPr>
@@ -1192,12 +1301,12 @@
   <sheetData>
     <row r="1" spans="1:28" ht="105.75" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B1" s="5" t="s"/>
       <c r="C1" s="5" t="s"/>
       <c r="D1" s="6" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E1" s="5" t="s"/>
       <c r="F1" s="15" t="s"/>
@@ -1235,7 +1344,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>4</v>
@@ -1491,7 +1600,7 @@
       </c>
       <c r="D13" s="5" t="s"/>
       <c r="E13" s="15" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="F13" s="16">
         <v>46305</v>
@@ -1510,7 +1619,7 @@
       </c>
       <c r="D14" s="5" t="s"/>
       <c r="E14" s="5" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="F14" s="16">
         <v>46305</v>
@@ -1529,7 +1638,7 @@
       </c>
       <c r="D15" s="5" t="s"/>
       <c r="E15" s="15" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="F15" s="16">
         <v>46305</v>
@@ -1548,7 +1657,7 @@
       </c>
       <c r="D16" s="5" t="s"/>
       <c r="E16" s="5" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="F16" s="16">
         <v>46305</v>
@@ -1586,7 +1695,7 @@
       </c>
       <c r="D18" s="27" t="s"/>
       <c r="E18" s="27" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="F18" s="28">
         <v>46307</v>
@@ -1604,7 +1713,7 @@
       </c>
       <c r="D19" s="27" t="s"/>
       <c r="E19" s="27" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="F19" s="28">
         <v>46309</v>
@@ -1677,7 +1786,7 @@
       </c>
       <c r="D23" s="5" t="s"/>
       <c r="E23" s="5" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="F23" s="16">
         <v>46309</v>
@@ -1695,7 +1804,7 @@
       </c>
       <c r="D24" s="5" t="s"/>
       <c r="E24" s="5" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="F24" s="16">
         <v>46309</v>
